--- a/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
+++ b/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Brazil/eps-brazil-3.4.2/InputData/trans/SYVbT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/trans/SYVbT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3F8073-9448-9842-A6CA-3A7096F37C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE5B510-5383-A742-993C-5F8E4430B36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="195">
   <si>
     <t>SYVbT Start Year Vehicles by Technology</t>
   </si>
@@ -608,6 +608,21 @@
   </si>
   <si>
     <t>PASSENGER</t>
+  </si>
+  <si>
+    <t>Climate Scorecard</t>
+  </si>
+  <si>
+    <t>The Growth of Electric Vehicles in Brazil: A Sustainable Revolution</t>
+  </si>
+  <si>
+    <t>https://www.climatescorecard.org/2025/03/the-growth-of-electric-vehicles-in-brazil-a-sustainable-revolution/#:~:text=Brazil%20registered%20around%20177%2C000%20electric,Charging%20Infrastructure</t>
+  </si>
+  <si>
+    <t>LDVs-Electric</t>
+  </si>
+  <si>
+    <t>2019-2024</t>
   </si>
 </sst>
 </file>
@@ -617,7 +632,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-10416]#,##0;\(#,##0\);&quot;0&quot;"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,8 +758,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -805,6 +827,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -844,7 +872,7 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -977,6 +1005,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1040,6 +1070,55 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D67D5314-7998-31DC-F725-7008E0FF99CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1803400" y="2501900"/>
+          <a:ext cx="19164300" cy="10820400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>624840</xdr:colOff>
       <xdr:row>5</xdr:row>
@@ -1085,7 +1164,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1332,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G982"/>
+  <dimension ref="A1:G985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" style="22" customWidth="1"/>
@@ -1581,127 +1660,98 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="64" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="65" t="s">
+        <v>191</v>
+      </c>
+    </row>
     <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="46" t="s">
+      <c r="B52" s="51">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B55" s="22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="47"/>
-      <c r="B53" s="22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="47"/>
-      <c r="B54" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" s="52"/>
-    </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="47"/>
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="47"/>
-      <c r="B56" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="48" t="s">
-        <v>19</v>
+      <c r="B56" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="47"/>
-      <c r="B57" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="F57" s="53" t="s">
-        <v>20</v>
-      </c>
+      <c r="B57" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="52"/>
     </row>
     <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="47"/>
-      <c r="B58" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" s="47"/>
-      <c r="F58" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="47"/>
-      <c r="B59" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="47"/>
-      <c r="F59" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G59" s="22" t="s">
-        <v>23</v>
+      <c r="B59" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="47"/>
-      <c r="B60" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="54"/>
-      <c r="F60" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>23</v>
+      <c r="B60" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="F60" s="53" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="47"/>
       <c r="B61" s="47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="54"/>
+        <v>22</v>
+      </c>
+      <c r="D61" s="47"/>
       <c r="F61" s="51" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="47"/>
       <c r="B62" s="47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D62" s="47"/>
       <c r="F62" s="51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G62" s="22" t="s">
         <v>23</v>
@@ -1710,14 +1760,14 @@
     <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="47"/>
       <c r="B63" s="47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="47"/>
+        <v>26</v>
+      </c>
+      <c r="D63" s="54"/>
       <c r="F63" s="51" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G63" s="22" t="s">
         <v>23</v>
@@ -1726,123 +1776,123 @@
     <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="47"/>
       <c r="B64" s="47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="D64" s="47"/>
+        <v>28</v>
+      </c>
+      <c r="D64" s="54"/>
       <c r="F64" s="51" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="47"/>
-      <c r="B65" s="47"/>
-      <c r="C65" s="47"/>
+      <c r="B65" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>30</v>
+      </c>
       <c r="D65" s="47"/>
+      <c r="F65" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="47"/>
-      <c r="B66" s="47"/>
-      <c r="C66" s="47"/>
+      <c r="B66" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D66" s="47"/>
+      <c r="F66" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="47"/>
-      <c r="B67" s="55"/>
-      <c r="C67" s="47"/>
+      <c r="B67" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D67" s="47"/>
+      <c r="F67" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="47"/>
-      <c r="B68" s="49" t="s">
-        <v>33</v>
-      </c>
+      <c r="B68" s="47"/>
       <c r="C68" s="47"/>
       <c r="D68" s="47"/>
-      <c r="F68" s="53" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="47"/>
-      <c r="B69" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
       <c r="D69" s="47"/>
-      <c r="F69" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G69" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="47"/>
-      <c r="B70" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B70" s="55"/>
+      <c r="C70" s="47"/>
       <c r="D70" s="47"/>
-      <c r="F70" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="47"/>
-      <c r="B71" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C71" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B71" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="47"/>
       <c r="D71" s="47"/>
-      <c r="F71" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G71" s="22" t="s">
-        <v>23</v>
+      <c r="F71" s="53" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="47"/>
       <c r="B72" s="47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C72" s="47" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D72" s="47"/>
       <c r="F72" s="51" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="47"/>
       <c r="B73" s="47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C73" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D73" s="47"/>
       <c r="F73" s="51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G73" s="22" t="s">
         <v>23</v>
@@ -1851,14 +1901,14 @@
     <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="47"/>
       <c r="B74" s="47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C74" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D74" s="47"/>
       <c r="F74" s="51" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G74" s="22" t="s">
         <v>23</v>
@@ -1867,117 +1917,117 @@
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="47"/>
       <c r="B75" s="47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D75" s="47"/>
       <c r="F75" s="51" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
+      <c r="B76" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D76" s="47"/>
+      <c r="F76" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="47"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="47"/>
+      <c r="B77" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D77" s="47"/>
+      <c r="F77" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="47"/>
-      <c r="B78" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="C78" s="47"/>
+      <c r="B78" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D78" s="47"/>
-      <c r="F78" s="53" t="s">
-        <v>36</v>
+      <c r="F78" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G78" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="47"/>
-      <c r="B79" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C79" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B79" s="47"/>
+      <c r="C79" s="47"/>
       <c r="D79" s="47"/>
-      <c r="F79" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G79" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="47"/>
-      <c r="B80" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C80" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B80" s="47"/>
+      <c r="C80" s="47"/>
       <c r="D80" s="47"/>
-      <c r="F80" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G80" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="47"/>
-      <c r="B81" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B81" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" s="47"/>
       <c r="D81" s="47"/>
-      <c r="F81" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="22" t="s">
-        <v>23</v>
+      <c r="F81" s="53" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="47"/>
       <c r="B82" s="47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D82" s="47"/>
       <c r="F82" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="G82" s="47" t="s">
-        <v>37</v>
+        <v>21</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="47"/>
       <c r="B83" s="47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C83" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D83" s="47"/>
       <c r="F83" s="51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G83" s="22" t="s">
         <v>23</v>
@@ -1986,14 +2036,14 @@
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="47"/>
       <c r="B84" s="47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C84" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D84" s="47"/>
       <c r="F84" s="51" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G84" s="22" t="s">
         <v>23</v>
@@ -2002,117 +2052,117 @@
     <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="47"/>
       <c r="B85" s="47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D85" s="47"/>
       <c r="F85" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="G85" s="22" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="G85" s="47" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="47"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
+      <c r="B86" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D86" s="47"/>
+      <c r="F86" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G86" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
+      <c r="B87" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D87" s="47"/>
+      <c r="F87" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G87" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="47"/>
-      <c r="B88" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" s="47"/>
+      <c r="B88" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C88" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D88" s="47"/>
-      <c r="F88" s="53" t="s">
-        <v>38</v>
+      <c r="F88" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G88" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="47"/>
-      <c r="B89" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C89" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="D89" s="54"/>
-      <c r="F89" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G89" s="22" t="s">
-        <v>23</v>
-      </c>
+      <c r="B89" s="47"/>
+      <c r="C89" s="47"/>
+      <c r="D89" s="47"/>
     </row>
     <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="47"/>
-      <c r="B90" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C90" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B90" s="47"/>
+      <c r="C90" s="47"/>
       <c r="D90" s="47"/>
-      <c r="F90" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G90" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="47"/>
-      <c r="B91" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C91" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B91" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C91" s="47"/>
       <c r="D91" s="47"/>
-      <c r="F91" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G91" s="22" t="s">
-        <v>23</v>
+      <c r="F91" s="53" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="47"/>
       <c r="B92" s="47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C92" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" s="54"/>
+      <c r="F92" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="22" t="s">
         <v>23</v>
-      </c>
-      <c r="D92" s="47"/>
-      <c r="F92" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="G92" s="47" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="47"/>
       <c r="B93" s="47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C93" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D93" s="47"/>
       <c r="F93" s="51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G93" s="22" t="s">
         <v>23</v>
@@ -2121,14 +2171,14 @@
     <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="47"/>
       <c r="B94" s="47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C94" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D94" s="47"/>
       <c r="F94" s="51" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G94" s="22" t="s">
         <v>23</v>
@@ -2137,117 +2187,117 @@
     <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="47"/>
       <c r="B95" s="47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C95" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D95" s="47"/>
       <c r="F95" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="G95" s="22" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="G95" s="47" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="47"/>
-      <c r="B96" s="47"/>
-      <c r="C96" s="47"/>
+      <c r="B96" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D96" s="47"/>
+      <c r="F96" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G96" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="97" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="47"/>
-      <c r="B97" s="47"/>
-      <c r="C97" s="47"/>
+      <c r="B97" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D97" s="47"/>
+      <c r="F97" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="98" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="47"/>
-      <c r="B98" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="C98" s="47"/>
+      <c r="B98" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C98" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D98" s="47"/>
-      <c r="F98" s="53" t="s">
-        <v>41</v>
+      <c r="F98" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G98" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="47"/>
-      <c r="B99" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C99" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
       <c r="D99" s="47"/>
-      <c r="F99" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G99" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="100" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="47"/>
-      <c r="B100" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C100" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
       <c r="D100" s="47"/>
-      <c r="F100" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G100" s="22" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="101" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="47"/>
-      <c r="B101" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C101" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B101" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="47"/>
       <c r="D101" s="47"/>
-      <c r="F101" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G101" s="22" t="s">
-        <v>23</v>
+      <c r="F101" s="53" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="47"/>
       <c r="B102" s="47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D102" s="47"/>
       <c r="F102" s="51" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="47"/>
       <c r="B103" s="47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C103" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="47"/>
       <c r="F103" s="51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>23</v>
@@ -2256,14 +2306,14 @@
     <row r="104" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="47"/>
       <c r="B104" s="47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C104" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D104" s="47"/>
       <c r="F104" s="51" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>23</v>
@@ -2272,86 +2322,101 @@
     <row r="105" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="47"/>
       <c r="B105" s="47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D105" s="47"/>
       <c r="F105" s="51" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="47"/>
-      <c r="B106" s="47"/>
-      <c r="C106" s="47"/>
+      <c r="B106" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D106" s="47"/>
+      <c r="F106" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G106" s="22" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="107" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="47"/>
-      <c r="B107" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C107" s="47"/>
+      <c r="B107" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D107" s="47"/>
-      <c r="F107" s="53" t="s">
-        <v>44</v>
+      <c r="F107" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="47"/>
       <c r="B108" s="47" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C108" s="47" t="s">
         <v>23</v>
       </c>
       <c r="D108" s="47"/>
-      <c r="F108" s="22" t="s">
-        <v>45</v>
+      <c r="F108" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G108" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="47"/>
-      <c r="B109" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C109" s="47" t="s">
-        <v>23</v>
-      </c>
+      <c r="B109" s="47"/>
+      <c r="C109" s="47"/>
       <c r="D109" s="47"/>
-      <c r="F109" s="51"/>
     </row>
     <row r="110" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="47"/>
-      <c r="B110" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C110" s="47" t="s">
-        <v>46</v>
-      </c>
+      <c r="B110" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" s="47"/>
       <c r="D110" s="47"/>
-      <c r="F110" s="51"/>
+      <c r="F110" s="53" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="111" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="47"/>
       <c r="B111" s="47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C111" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D111" s="54"/>
-      <c r="F111" s="51"/>
+      <c r="D111" s="47"/>
+      <c r="F111" s="22" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="112" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="47"/>
       <c r="B112" s="47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C112" s="47" t="s">
         <v>23</v>
@@ -2360,43 +2425,73 @@
       <c r="F112" s="51"/>
     </row>
     <row r="113" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="47"/>
       <c r="B113" s="47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D113" s="47"/>
       <c r="F113" s="51"/>
     </row>
     <row r="114" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="47"/>
       <c r="B114" s="47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C114" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D114" s="47"/>
+      <c r="D114" s="54"/>
       <c r="F114" s="51"/>
     </row>
     <row r="115" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B115" s="47"/>
-      <c r="C115" s="47"/>
+      <c r="A115" s="47"/>
+      <c r="B115" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" s="47" t="s">
+        <v>23</v>
+      </c>
       <c r="D115" s="47"/>
       <c r="F115" s="51"/>
     </row>
     <row r="116" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="22" t="s">
+      <c r="B116" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" s="47"/>
+      <c r="F116" s="51"/>
+    </row>
+    <row r="117" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B117" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" s="47"/>
+      <c r="F117" s="51"/>
+    </row>
+    <row r="118" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B118" s="47"/>
+      <c r="C118" s="47"/>
+      <c r="D118" s="47"/>
+      <c r="F118" s="51"/>
+    </row>
+    <row r="119" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B116" s="52">
+      <c r="B119" s="52">
         <v>2017</v>
       </c>
-      <c r="D116" s="47"/>
-    </row>
-    <row r="117" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="D119" s="47"/>
+    </row>
     <row r="120" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="121" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="122" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2438,45 +2533,45 @@
     <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A176" s="22" t="s">
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A179" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B176" s="22">
+      <c r="B179" s="22">
         <v>2015</v>
       </c>
     </row>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -3267,6 +3362,9 @@
     <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -3277,6 +3375,7 @@
     <hyperlink ref="B7" r:id="rId6" xr:uid="{9CF57686-F62F-42F5-833A-50C2630C0CDF}"/>
     <hyperlink ref="B29" r:id="rId7" xr:uid="{1EBF0924-DE10-4A22-B609-281ACBE98FFF}"/>
     <hyperlink ref="C30" r:id="rId8" xr:uid="{5928296F-03A8-4F9C-BCCA-D197C96E760E}"/>
+    <hyperlink ref="B53" r:id="rId9" location=":~:text=Brazil%20registered%20around%20177%2C000%20electric,Charging%20Infrastructure" xr:uid="{A6D9E357-215E-4747-835F-C2365F39D7EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -3650,8 +3749,7 @@
         <v>62</v>
       </c>
       <c r="B7" s="15">
-        <f>$Y$4*G51</f>
-        <v>0</v>
+        <v>6202356</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>55</v>
@@ -7887,7 +7985,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C016339-8CE9-49FD-97E9-BE5E7ED4DAEB}">
-  <dimension ref="B2:F13"/>
+  <dimension ref="A2:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.15">
@@ -8087,8 +8185,22 @@
         <v>110</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B17" s="48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18">
+        <v>41000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9629,17 +9741,18 @@
         <v>20</v>
       </c>
       <c r="B2" s="11">
-        <f>EV!E8</f>
-        <v>1217</v>
+        <f>EV!B18</f>
+        <v>41000</v>
       </c>
       <c r="C2" s="11">
         <v>0</v>
       </c>
       <c r="D2" s="11">
-        <f>SUM(Road!B4:B7,Road!B9:B11)</f>
-        <v>43287261.815512933</v>
+        <f>SUM(Road!B4,Road!B7,Road!B9,Road!B5,Road!B10,Road!B11)</f>
+        <v>17139364.113129884</v>
       </c>
       <c r="E2" s="11">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="F2" s="11">
@@ -10790,6 +10903,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <ignoredErrors>
+    <ignoredError sqref="F2" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
